--- a/data/trans_orig/IP07C12-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C12-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2007 (tasa de respuesta: 89,59%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2007 (tasa de respuesta: 89,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51450</t>
+          <t>51783</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68525</t>
+          <t>68907</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49518</t>
+          <t>49754</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67424</t>
+          <t>66932</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107302</t>
+          <t>107110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132535</t>
+          <t>131469</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25338</t>
+          <t>25380</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40939</t>
+          <t>40714</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37906</t>
+          <t>37675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55243</t>
+          <t>55015</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66050</t>
+          <t>66682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89908</t>
+          <t>90140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>22079</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11839</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24430</t>
+          <t>24449</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42012</t>
+          <t>43565</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77768</t>
+          <t>77206</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98783</t>
+          <t>98242</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97449</t>
+          <t>98237</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119713</t>
+          <t>119257</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181955</t>
+          <t>182879</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210667</t>
+          <t>211959</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,28%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56544</t>
+          <t>57451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77152</t>
+          <t>77922</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42706</t>
+          <t>42929</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62161</t>
+          <t>62123</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104594</t>
+          <t>104376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132202</t>
+          <t>132917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25393</t>
+          <t>25825</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17852</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32124</t>
+          <t>32412</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>34442</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53685</t>
+          <t>53196</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>135123</t>
+          <t>135102</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161467</t>
+          <t>162667</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>153625</t>
+          <t>153294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181696</t>
+          <t>180354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>295884</t>
+          <t>296265</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>335569</t>
+          <t>334936</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85801</t>
+          <t>85757</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111881</t>
+          <t>112550</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85040</t>
+          <t>85103</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111845</t>
+          <t>111615</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,47 +2259,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>36,13%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>196888</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>178597</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>216615</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>32,91%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>29,86%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>36,21%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>196888</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>179401</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>215682</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>32,91%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>29,99%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44441</t>
+          <t>44105</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33025</t>
+          <t>32011</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51994</t>
+          <t>52021</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64606</t>
+          <t>64283</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>89667</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82272</t>
+          <t>81509</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101306</t>
+          <t>101592</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76762</t>
+          <t>75501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97713</t>
+          <t>96946</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>163819</t>
+          <t>163163</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>192026</t>
+          <t>192070</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,08%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32852</t>
+          <t>32197</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50935</t>
+          <t>50956</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40820</t>
+          <t>41596</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60630</t>
+          <t>61085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>78620</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105515</t>
+          <t>106530</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>21184</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>12429</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26072</t>
+          <t>26272</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24203</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41554</t>
+          <t>42731</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71435</t>
+          <t>70170</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92343</t>
+          <t>92804</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86181</t>
+          <t>84190</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107840</t>
+          <t>105545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>162358</t>
+          <t>161979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191600</t>
+          <t>193160</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>58,03%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45075</t>
+          <t>45564</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64683</t>
+          <t>64933</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47377</t>
+          <t>49124</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68444</t>
+          <t>69298</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100072</t>
+          <t>100179</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128435</t>
+          <t>128077</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16172</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31708</t>
+          <t>31297</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19460</t>
+          <t>20499</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27137</t>
+          <t>27674</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46041</t>
+          <t>47386</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5548</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2450</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10755</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>159390</t>
+          <t>159205</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188044</t>
+          <t>187305</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>168737</t>
+          <t>167659</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197669</t>
+          <t>197700</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>335458</t>
+          <t>335088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>375621</t>
+          <t>375950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83211</t>
+          <t>83959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111135</t>
+          <t>110781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95524</t>
+          <t>95968</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122069</t>
+          <t>122949</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,47 +4535,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>29,43%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>37,71%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>205119</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>186679</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>225558</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>32,18%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>29,29%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>37,44%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>205119</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>185450</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>224222</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>32,18%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>29,1%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28234</t>
+          <t>28396</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47554</t>
+          <t>47528</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23949</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41998</t>
+          <t>41613</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>57307</t>
+          <t>56242</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83439</t>
+          <t>81717</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2016 (tasa de respuesta: 95,18%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2016 (tasa de respuesta: 95,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86509</t>
+          <t>86632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108330</t>
+          <t>109534</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91988</t>
+          <t>92169</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113737</t>
+          <t>113752</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>186776</t>
+          <t>187595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>217045</t>
+          <t>218134</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>61,0%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45690</t>
+          <t>45973</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65673</t>
+          <t>66485</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49349</t>
+          <t>49212</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71164</t>
+          <t>70686</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100219</t>
+          <t>101479</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128739</t>
+          <t>130378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15273</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29673</t>
+          <t>28192</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22271</t>
+          <t>22513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28005</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>46954</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>705</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73704</t>
+          <t>72277</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96624</t>
+          <t>94390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73829</t>
+          <t>73447</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95074</t>
+          <t>95998</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154690</t>
+          <t>152657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185493</t>
+          <t>184322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,33%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48446</t>
+          <t>49927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69618</t>
+          <t>71182</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53933</t>
+          <t>53124</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74855</t>
+          <t>74185</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108294</t>
+          <t>109669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139285</t>
+          <t>139499</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23832</t>
+          <t>23794</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>11046</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23839</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25214</t>
+          <t>25340</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43768</t>
+          <t>43546</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>167410</t>
+          <t>167370</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>198310</t>
+          <t>197316</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>170115</t>
+          <t>172859</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204679</t>
+          <t>203809</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>347809</t>
+          <t>349969</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>392516</t>
+          <t>393692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99899</t>
+          <t>101754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129428</t>
+          <t>131135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>107432</t>
+          <t>107317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138193</t>
+          <t>137237</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>217401</t>
+          <t>217072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>259018</t>
+          <t>259367</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28568</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48037</t>
+          <t>48060</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24330</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42482</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56949</t>
+          <t>58028</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83184</t>
+          <t>84058</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -7100,54 +7100,54 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5545</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5449</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C12-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C12-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2007 (tasa de respuesta: 89,59%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella, percibida por el/la menor en 2007 (tasa de respuesta: 89,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,67 +727,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>58583</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>49444</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>67871</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47,71%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40,26%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>60347</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>51783</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>68907</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>51851</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>68220</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>54,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>61,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>58583</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>49754</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>66932</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>47,71%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107110</t>
+          <t>106741</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131469</t>
+          <t>132075</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46196</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37601</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>55357</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,08%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>32252</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>25380</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>40714</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>25343</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>41069</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>28,87%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>36,45%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>46196</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>37675</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>55015</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>37,62%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66682</t>
+          <t>65829</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90140</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17446</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11600</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24568</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14,21%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20,01%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15795</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10425</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22079</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>10235</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>22483</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>14,14%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17446</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12140</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24449</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25614</t>
+          <t>24041</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43565</t>
+          <t>41197</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3495</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2676</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6660</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6716</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,4%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3117</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1174,107 +1174,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3862</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3840</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3325</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3596</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122802</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122802</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122802</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>122802</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>122802</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>122802</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>108755</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>98168</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>119490</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52,75%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>64,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>87923</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>77206</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>98242</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>76788</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>98162</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>49,51%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>108755</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>98237</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>119257</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>58,44%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>182879</t>
+          <t>181503</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>211959</t>
+          <t>210850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,97%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>51531</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>42802</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>61311</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>23,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>32,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66910</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57451</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77922</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>58361</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>78448</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>37,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>32,35%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,88%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>51531</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>42929</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>62123</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>27,69%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104376</t>
+          <t>104239</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132917</t>
+          <t>134507</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>24425</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17511</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32816</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13,12%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17,63%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>18575</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12029</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>25825</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12886</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>25558</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10,46%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,54%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>24425</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>17780</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>32412</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>13,12%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34442</t>
+          <t>33502</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53196</t>
+          <t>52999</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4118</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3504</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8403</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7451</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4287</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1861,102 +1861,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3889</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3465</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3452</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3381</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5233</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4731</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>177598</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>177598</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>177598</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>167338</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>152366</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>180870</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>54,17%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>49,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>58,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>148270</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>135102</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>162667</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>134090</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>161422</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>51,25%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>46,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>167338</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>153294</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>180354</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>54,17%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>296265</t>
+          <t>296662</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>334936</t>
+          <t>335383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>97726</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>84406</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>110749</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>27,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35,85%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>99162</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>85757</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>112550</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>87203</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>113039</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,28%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>29,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,9%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>97726</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>85103</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>111615</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>31,64%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>178597</t>
+          <t>179011</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216615</t>
+          <t>214171</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>41870</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>33249</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>51467</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>13,55%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>34369</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>25806</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>44105</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>26625</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>43831</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>11,88%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,24%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>41870</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>32011</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>52021</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>13,55%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64283</t>
+          <t>63319</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>89667</t>
+          <t>88779</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4700</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>6179</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2914</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>11223</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>12295</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,14%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1297</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4602</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12879</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3489</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1328</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4647</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4619</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3171</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>308899</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>308899</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>308899</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>430</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>289309</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>289309</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>289309</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>308899</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>308899</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>308899</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella, percibida por el/la menor en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>86185</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>74752</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>95796</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>55,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>48,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,63%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>92042</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>81509</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>101592</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>81552</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>101014</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>61,75%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>68,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>86185</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>75501</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>96946</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>55,45%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>163163</t>
+          <t>164682</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>192070</t>
+          <t>192370</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50821</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41784</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>61366</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32,7%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,88%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>41350</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>32197</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>50956</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>32011</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>50560</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>27,74%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,19%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>50821</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>41596</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61085</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>32,7%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78620</t>
+          <t>78717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106530</t>
+          <t>105076</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18421</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12433</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>25929</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,85%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,68%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>13920</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8761</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21184</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9008</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>20764</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>9,34%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>18421</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12429</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>26272</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23898</t>
+          <t>24784</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42731</t>
+          <t>43202</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -3337,107 +3337,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1737</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6069</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5379</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1737</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5849</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149049</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>149049</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>149049</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>96085</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>85425</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>106005</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>62,12%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>81846</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>70170</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>92804</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>71093</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>92702</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>50,46%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>96085</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>84190</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>105545</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>56,3%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161979</t>
+          <t>163337</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193160</t>
+          <t>191926</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,66%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>58127</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>48523</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>68547</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,43%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>54821</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>45564</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>64933</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>44809</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>64631</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>33,8%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>58127</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>49124</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>69298</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,06%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100179</t>
+          <t>98585</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128077</t>
+          <t>126619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13235</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8633</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>20201</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,84%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>23269</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16828</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>31297</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>16389</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>31539</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>14,34%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,29%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>13235</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>8714</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>20499</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27674</t>
+          <t>28254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47386</t>
+          <t>46857</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7266</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2274</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6531</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6121</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7245</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>182270</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>168828</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>197041</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>55,9%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>51,78%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>60,43%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>173888</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>159205</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>187305</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>158923</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>188447</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>55,87%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>51,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>60,18%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>182270</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>167659</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>197700</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>55,9%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>335088</t>
+          <t>336027</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>375950</t>
+          <t>377882</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>108948</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>96215</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>123237</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,41%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29,51%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,79%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>96170</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>83959</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>110781</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>83078</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>108714</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>30,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,97%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>35,59%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>108948</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>95968</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>122949</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>33,41%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186679</t>
+          <t>184502</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>225558</t>
+          <t>224810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>31656</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>22942</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>40877</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,54%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>37189</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>28396</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>47528</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>28817</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>48212</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>11,95%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>31656</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>23293</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>41613</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56242</t>
+          <t>57099</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>81717</t>
+          <t>83736</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -4706,67 +4706,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6992</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>4012</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8894</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1473</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8568</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7999</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>311258</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>311258</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>311258</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2016 (tasa de respuesta: 95,18%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella, percibida por el/la menor en 2016 (tasa de respuesta: 95,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>103422</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>92004</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>114420</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>57,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>51,51%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>64,06%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>98282</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>86632</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>109534</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>86351</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>108902</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>54,92%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>48,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>61,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>103422</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>92169</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>113752</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>57,9%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>187595</t>
+          <t>185470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>218134</t>
+          <t>216867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,65%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59118</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>49772</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>71162</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>33,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,87%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55490</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45973</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>66485</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>45576</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>66510</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31,01%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59118</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>49212</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>70686</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>33,1%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101479</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130378</t>
+          <t>130363</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15444</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10241</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22653</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,68%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>21181</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14406</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>28192</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>14988</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>28913</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>11,84%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,75%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>15444</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9878</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>22513</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27884</t>
+          <t>27655</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46954</t>
+          <t>46148</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -5613,107 +5613,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3357</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2795</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6986</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6521</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3351</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>3421</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>7698</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3421</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>7579</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -5726,107 +5726,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1218</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4237</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3767</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,68%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3766</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4245</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>178967</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>178967</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>178967</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84916</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>74704</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>95609</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>50,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>84588</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>72277</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>94390</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>73079</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>94863</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,33%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,86%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>84916</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>73447</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>95998</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>50,45%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152657</t>
+          <t>154806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184322</t>
+          <t>184484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,38%</t>
         </is>
       </c>
     </row>
@@ -6074,67 +6074,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>64051</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53675</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75169</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,66%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>59784</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>49927</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>71182</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>49251</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>70880</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>36,28%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>64051</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>53124</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>74185</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>38,05%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109669</t>
+          <t>109531</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139499</t>
+          <t>138832</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16900</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>24098</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10,04%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,32%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>16386</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10523</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23794</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>11189</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>23822</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>9,94%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,44%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>16900</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>11046</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>24283</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>10,04%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25340</t>
+          <t>24397</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43546</t>
+          <t>42662</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -6295,74 +6295,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2446</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6360</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3343</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1098</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7480</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1226</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7488</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,03%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>4,54%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2446</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7768</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10608</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -6408,107 +6408,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>706</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3782</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3526</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3519</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3985</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>168313</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>168313</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>168313</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>188339</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>173687</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>202990</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>54,29%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>50,06%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>58,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>182870</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>167370</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>197316</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>168287</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>200294</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>53,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,69%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>57,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>188339</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>172859</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>203809</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>54,29%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>349969</t>
+          <t>349956</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>393692</t>
+          <t>394399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>123169</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>107337</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>137580</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,5%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>30,94%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>115274</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>101754</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>131135</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>100742</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>131459</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>33,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>29,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>123169</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>107317</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>137237</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>35,5%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>217072</t>
+          <t>215634</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>259367</t>
+          <t>259216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>32344</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>24407</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>41874</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>37567</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>28455</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>48060</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>28704</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>48385</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>10,93%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>13,98%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>32344</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>24820</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>42412</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58028</t>
+          <t>57328</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84058</t>
+          <t>84693</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3072</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7531</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>6138</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2904</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>11489</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>3177</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>11501</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3072</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7801</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1925</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5545</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5118</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>346924</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>346924</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>346924</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>490</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>343774</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>343774</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>343774</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>346924</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>346924</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>346924</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
